--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kojo1910-my.sharepoint.com/personal/y-suga_kojo_ed_jp/Documents/DATA/資料室/【Private】/横浜保土ケ谷区民吹奏楽団/広報/web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_AD4D066CA252ABDACC104872B1D0DFB873EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D6619B-8D23-4CEC-A169-F9AE71E8173A}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="11_AD4D066CA252ABDACC104872B1D0DFB873EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B2B74F7-6DC4-4AF2-B9A8-D1A368C1C339}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
   <si>
     <t>日にち</t>
     <rPh sb="0" eb="1">
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>17:30 ～ 21:00</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>保土ケ谷公会堂（会議室）</t>
     <rPh sb="0" eb="7">
       <t>ホドガヤコウカイドウ</t>
@@ -165,6 +161,39 @@
     </rPh>
     <rPh sb="4" eb="9">
       <t>テイキエンソウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保土ケ谷公会堂（会議室）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10/12 ㈪ ㊗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>役員会</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクイン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10/10 ㈯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:30 ～ 22:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>役員会</t>
+    <rPh sb="0" eb="3">
+      <t>ヤクインカイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -380,6 +409,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -645,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="10.69921875" style="7" customWidth="1"/>
@@ -671,142 +704,170 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="16" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>15</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
